--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="186">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -591,6 +591,12 @@
   </si>
   <si>
     <t>جمع کل حساب با احتساب آخرین فاکتور :</t>
+  </si>
+  <si>
+    <t>1405/04/13</t>
+  </si>
+  <si>
+    <t>دنگ بوته</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1102,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>351500</v>
+        <v>993500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3121,17 +3127,23 @@
     <row r="145" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="7">
         <f>A144+B145-C145</f>
-        <v>351500</v>
-      </c>
-      <c r="B145" s="7"/>
+        <v>993500</v>
+      </c>
+      <c r="B145" s="7">
+        <v>642000</v>
+      </c>
       <c r="C145" s="7"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="1"/>
+      <c r="D145" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="146" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="7">
         <f t="shared" ref="A146:A158" si="7">A145+B146-C146</f>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
@@ -3141,7 +3153,7 @@
     <row r="147" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -3151,7 +3163,7 @@
     <row r="148" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
@@ -3161,7 +3173,7 @@
     <row r="149" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
@@ -3171,7 +3183,7 @@
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -3181,7 +3193,7 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -3191,7 +3203,7 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -3201,7 +3213,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -3211,7 +3223,7 @@
     <row r="154" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -3221,7 +3233,7 @@
     <row r="155" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -3231,7 +3243,7 @@
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3241,7 +3253,7 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3251,7 +3263,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3262,7 +3274,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>11086500</v>
+        <v>11728500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3274,7 +3286,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>351500</v>
+        <v>993500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="187">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -597,6 +597,9 @@
   </si>
   <si>
     <t>دنگ بوته</t>
+  </si>
+  <si>
+    <t>1405/04/14</t>
   </si>
 </sst>
 </file>
@@ -1102,7 +1105,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3143,17 +3146,23 @@
     <row r="146" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="7">
         <f t="shared" ref="A146:A158" si="7">A145+B146-C146</f>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B146" s="7"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="1"/>
+      <c r="C146" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="147" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -3163,7 +3172,7 @@
     <row r="148" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
@@ -3173,7 +3182,7 @@
     <row r="149" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
@@ -3183,7 +3192,7 @@
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -3193,7 +3202,7 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -3203,7 +3212,7 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -3213,7 +3222,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -3223,7 +3232,7 @@
     <row r="154" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -3233,7 +3242,7 @@
     <row r="155" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -3243,7 +3252,7 @@
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3253,7 +3262,7 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3263,7 +3272,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3278,7 +3287,7 @@
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
-        <v>10735000</v>
+        <v>11735000</v>
       </c>
       <c r="D159" s="8"/>
     </row>
@@ -3286,7 +3295,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>993500</v>
+        <v>-6500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="187">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3162,17 +3162,23 @@
     <row r="147" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
-      </c>
-      <c r="B147" s="7"/>
+        <v>210500</v>
+      </c>
+      <c r="B147" s="7">
+        <v>217000</v>
+      </c>
       <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="1"/>
+      <c r="D147" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="148" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
@@ -3182,7 +3188,7 @@
     <row r="149" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
@@ -3192,7 +3198,7 @@
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -3202,7 +3208,7 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -3212,7 +3218,7 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -3222,7 +3228,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -3232,7 +3238,7 @@
     <row r="154" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -3242,7 +3248,7 @@
     <row r="155" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -3252,7 +3258,7 @@
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3262,7 +3268,7 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3272,7 +3278,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3283,7 +3289,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>11728500</v>
+        <v>11945500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3295,7 +3301,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>-6500</v>
+        <v>210500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="188">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -600,6 +600,9 @@
   </si>
   <si>
     <t>1405/04/14</t>
+  </si>
+  <si>
+    <t>مزه</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1108,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>210500</v>
+        <v>485500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3178,19 +3181,25 @@
     <row r="148" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="7">
         <f t="shared" si="7"/>
-        <v>210500</v>
-      </c>
-      <c r="B148" s="7"/>
+        <v>450500</v>
+      </c>
+      <c r="B148" s="7">
+        <v>240000</v>
+      </c>
       <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
+      <c r="D148" s="7" t="s">
+        <v>187</v>
+      </c>
       <c r="E148" s="1"/>
     </row>
     <row r="149" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="7">
         <f t="shared" si="7"/>
-        <v>210500</v>
-      </c>
-      <c r="B149" s="7"/>
+        <v>485500</v>
+      </c>
+      <c r="B149" s="7">
+        <v>35000</v>
+      </c>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
       <c r="E149" s="1"/>
@@ -3198,7 +3207,7 @@
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="7">
         <f t="shared" si="7"/>
-        <v>210500</v>
+        <v>485500</v>
       </c>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -3208,7 +3217,7 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <f t="shared" si="7"/>
-        <v>210500</v>
+        <v>485500</v>
       </c>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -3218,7 +3227,7 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <f t="shared" si="7"/>
-        <v>210500</v>
+        <v>485500</v>
       </c>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -3228,7 +3237,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <f t="shared" si="7"/>
-        <v>210500</v>
+        <v>485500</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -3238,7 +3247,7 @@
     <row r="154" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <f t="shared" si="7"/>
-        <v>210500</v>
+        <v>485500</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -3248,7 +3257,7 @@
     <row r="155" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <f t="shared" si="7"/>
-        <v>210500</v>
+        <v>485500</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -3258,7 +3267,7 @@
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>210500</v>
+        <v>485500</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3268,7 +3277,7 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>210500</v>
+        <v>485500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3278,7 +3287,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>210500</v>
+        <v>485500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3289,7 +3298,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>11945500</v>
+        <v>12220500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3301,7 +3310,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>210500</v>
+        <v>485500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="188">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>485500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3207,17 +3207,21 @@
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="7">
         <f t="shared" si="7"/>
-        <v>485500</v>
+        <v>5500</v>
       </c>
       <c r="B150" s="7"/>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
+      <c r="C150" s="7">
+        <v>480000</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="E150" s="1"/>
     </row>
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <f t="shared" si="7"/>
-        <v>485500</v>
+        <v>5500</v>
       </c>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -3227,7 +3231,7 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <f t="shared" si="7"/>
-        <v>485500</v>
+        <v>5500</v>
       </c>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -3237,7 +3241,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <f t="shared" si="7"/>
-        <v>485500</v>
+        <v>5500</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -3247,7 +3251,7 @@
     <row r="154" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <f t="shared" si="7"/>
-        <v>485500</v>
+        <v>5500</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -3257,7 +3261,7 @@
     <row r="155" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <f t="shared" si="7"/>
-        <v>485500</v>
+        <v>5500</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -3267,7 +3271,7 @@
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>485500</v>
+        <v>5500</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3277,7 +3281,7 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>485500</v>
+        <v>5500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3287,7 +3291,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>485500</v>
+        <v>5500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3302,7 +3306,7 @@
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
-        <v>11735000</v>
+        <v>12215000</v>
       </c>
       <c r="D159" s="8"/>
     </row>
@@ -3310,7 +3314,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>485500</v>
+        <v>5500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="189">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -603,6 +603,9 @@
   </si>
   <si>
     <t>مزه</t>
+  </si>
+  <si>
+    <t>مزه حسین</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1111,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>5500</v>
+        <v>125500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3221,17 +3224,21 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <f t="shared" si="7"/>
-        <v>5500</v>
-      </c>
-      <c r="B151" s="7"/>
+        <v>125500</v>
+      </c>
+      <c r="B151" s="7">
+        <v>120000</v>
+      </c>
       <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
+      <c r="D151" s="7" t="s">
+        <v>188</v>
+      </c>
       <c r="E151" s="1"/>
     </row>
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <f t="shared" si="7"/>
-        <v>5500</v>
+        <v>125500</v>
       </c>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -3241,7 +3248,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <f t="shared" si="7"/>
-        <v>5500</v>
+        <v>125500</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -3251,7 +3258,7 @@
     <row r="154" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <f t="shared" si="7"/>
-        <v>5500</v>
+        <v>125500</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -3261,7 +3268,7 @@
     <row r="155" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <f t="shared" si="7"/>
-        <v>5500</v>
+        <v>125500</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -3271,7 +3278,7 @@
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>5500</v>
+        <v>125500</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3281,7 +3288,7 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>5500</v>
+        <v>125500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3291,7 +3298,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>5500</v>
+        <v>125500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3302,7 +3309,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>12220500</v>
+        <v>12340500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3314,7 +3321,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>5500</v>
+        <v>125500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="189">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -605,7 +605,7 @@
     <t>مزه</t>
   </si>
   <si>
-    <t>مزه حسین</t>
+    <t xml:space="preserve">لواشک بستنی </t>
   </si>
 </sst>
 </file>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>125500</v>
+        <v>35500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3224,10 +3224,10 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <f t="shared" si="7"/>
-        <v>125500</v>
+        <v>235500</v>
       </c>
       <c r="B151" s="7">
-        <v>120000</v>
+        <v>230000</v>
       </c>
       <c r="C151" s="7"/>
       <c r="D151" s="7" t="s">
@@ -3238,17 +3238,21 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <f t="shared" si="7"/>
-        <v>125500</v>
+        <v>35500</v>
       </c>
       <c r="B152" s="7"/>
-      <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
+      <c r="C152" s="7">
+        <v>200000</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="E152" s="1"/>
     </row>
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <f t="shared" si="7"/>
-        <v>125500</v>
+        <v>35500</v>
       </c>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -3258,7 +3262,7 @@
     <row r="154" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <f t="shared" si="7"/>
-        <v>125500</v>
+        <v>35500</v>
       </c>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -3268,7 +3272,7 @@
     <row r="155" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <f t="shared" si="7"/>
-        <v>125500</v>
+        <v>35500</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -3278,7 +3282,7 @@
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>125500</v>
+        <v>35500</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3288,7 +3292,7 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>125500</v>
+        <v>35500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3298,7 +3302,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>125500</v>
+        <v>35500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3309,11 +3313,11 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>12340500</v>
+        <v>12450500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
-        <v>12215000</v>
+        <v>12415000</v>
       </c>
       <c r="D159" s="8"/>
     </row>
@@ -3321,7 +3325,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>125500</v>
+        <v>35500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="192">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -606,6 +606,15 @@
   </si>
   <si>
     <t xml:space="preserve">لواشک بستنی </t>
+  </si>
+  <si>
+    <t>1405/04/19</t>
+  </si>
+  <si>
+    <t>دنگ کیک رضا</t>
+  </si>
+  <si>
+    <t>ساندویچ باغتون</t>
   </si>
 </sst>
 </file>
@@ -1111,7 +1120,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>35500</v>
+        <v>266500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3252,27 +3261,37 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <f t="shared" si="7"/>
-        <v>35500</v>
-      </c>
-      <c r="B153" s="7"/>
+        <v>120500</v>
+      </c>
+      <c r="B153" s="7">
+        <v>85000</v>
+      </c>
       <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="1"/>
+      <c r="D153" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="154" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <f t="shared" si="7"/>
-        <v>35500</v>
-      </c>
-      <c r="B154" s="7"/>
+        <v>266500</v>
+      </c>
+      <c r="B154" s="7">
+        <v>146000</v>
+      </c>
       <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
+      <c r="D154" s="7" t="s">
+        <v>191</v>
+      </c>
       <c r="E154" s="1"/>
     </row>
     <row r="155" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <f t="shared" si="7"/>
-        <v>35500</v>
+        <v>266500</v>
       </c>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -3282,7 +3301,7 @@
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>35500</v>
+        <v>266500</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3292,7 +3311,7 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>35500</v>
+        <v>266500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3302,7 +3321,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>35500</v>
+        <v>266500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3313,7 +3332,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>12450500</v>
+        <v>12681500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3325,7 +3344,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>35500</v>
+        <v>266500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="193">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -615,6 +615,9 @@
   </si>
   <si>
     <t>ساندویچ باغتون</t>
+  </si>
+  <si>
+    <t>کیک تخم شربتی</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1123,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>266500</v>
+        <v>356500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3291,17 +3294,21 @@
     <row r="155" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <f t="shared" si="7"/>
-        <v>266500</v>
-      </c>
-      <c r="B155" s="7"/>
+        <v>356500</v>
+      </c>
+      <c r="B155" s="7">
+        <v>90000</v>
+      </c>
       <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
+      <c r="D155" s="7" t="s">
+        <v>192</v>
+      </c>
       <c r="E155" s="1"/>
     </row>
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>266500</v>
+        <v>356500</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3311,7 +3318,7 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>266500</v>
+        <v>356500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3321,7 +3328,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>266500</v>
+        <v>356500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3332,7 +3339,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>12681500</v>
+        <v>12771500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3344,7 +3351,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>266500</v>
+        <v>356500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="192">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -615,9 +615,6 @@
   </si>
   <si>
     <t>ساندویچ باغتون</t>
-  </si>
-  <si>
-    <t>کیک تخم شربتی</t>
   </si>
 </sst>
 </file>
@@ -1123,7 +1120,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>356500</v>
+        <v>266500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3294,21 +3291,17 @@
     <row r="155" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <f t="shared" si="7"/>
-        <v>356500</v>
-      </c>
-      <c r="B155" s="7">
-        <v>90000</v>
-      </c>
+        <v>266500</v>
+      </c>
+      <c r="B155" s="7"/>
       <c r="C155" s="7"/>
-      <c r="D155" s="7" t="s">
-        <v>192</v>
-      </c>
+      <c r="D155" s="7"/>
       <c r="E155" s="1"/>
     </row>
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>356500</v>
+        <v>266500</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3318,7 +3311,7 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>356500</v>
+        <v>266500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3328,7 +3321,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>356500</v>
+        <v>266500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3339,7 +3332,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>12771500</v>
+        <v>12681500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3351,7 +3344,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>356500</v>
+        <v>266500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="194">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -615,6 +615,12 @@
   </si>
   <si>
     <t>ساندویچ باغتون</t>
+  </si>
+  <si>
+    <t>1405/05/02</t>
+  </si>
+  <si>
+    <t>کوصشریات</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1126,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>266500</v>
+        <v>646500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3291,17 +3297,23 @@
     <row r="155" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <f t="shared" si="7"/>
-        <v>266500</v>
-      </c>
-      <c r="B155" s="7"/>
+        <v>646500</v>
+      </c>
+      <c r="B155" s="7">
+        <v>380000</v>
+      </c>
       <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="1"/>
+      <c r="D155" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>266500</v>
+        <v>646500</v>
       </c>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3311,7 +3323,7 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>266500</v>
+        <v>646500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3321,7 +3333,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>266500</v>
+        <v>646500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3332,7 +3344,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>12681500</v>
+        <v>13061500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3344,7 +3356,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>266500</v>
+        <v>646500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="196">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -621,6 +621,12 @@
   </si>
   <si>
     <t>کوصشریات</t>
+  </si>
+  <si>
+    <t>1405/05/30</t>
+  </si>
+  <si>
+    <t>ابمیوه کیک چسپس</t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1132,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>646500</v>
+        <v>866500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3313,17 +3319,23 @@
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>646500</v>
-      </c>
-      <c r="B156" s="7"/>
+        <v>866500</v>
+      </c>
+      <c r="B156" s="7">
+        <v>220000</v>
+      </c>
       <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="1"/>
+      <c r="D156" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>646500</v>
+        <v>866500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3333,7 +3345,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>646500</v>
+        <v>866500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3344,7 +3356,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>13061500</v>
+        <v>13281500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3356,7 +3368,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>646500</v>
+        <v>866500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="198">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -627,6 +627,12 @@
   </si>
   <si>
     <t>ابمیوه کیک چسپس</t>
+  </si>
+  <si>
+    <t>1405/06/09</t>
+  </si>
+  <si>
+    <t>مزه پل دوآب</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1138,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>866500</v>
+        <v>1036500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3335,17 +3341,23 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>866500</v>
-      </c>
-      <c r="B157" s="7"/>
+        <v>1036500</v>
+      </c>
+      <c r="B157" s="7">
+        <v>170000</v>
+      </c>
       <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="1"/>
+      <c r="D157" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>866500</v>
+        <v>1036500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3356,7 +3368,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>13281500</v>
+        <v>13451500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3368,7 +3380,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>866500</v>
+        <v>1036500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="199">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -633,6 +633,9 @@
   </si>
   <si>
     <t>مزه پل دوآب</t>
+  </si>
+  <si>
+    <t>بستنی اسنک چیپلت</t>
   </si>
 </sst>
 </file>
@@ -1138,7 +1141,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>1036500</v>
+        <v>1321500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3357,18 +3360,22 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>1036500</v>
-      </c>
-      <c r="B158" s="7"/>
+        <v>1321500</v>
+      </c>
+      <c r="B158" s="7">
+        <v>285000</v>
+      </c>
       <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
+      <c r="D158" s="7" t="s">
+        <v>198</v>
+      </c>
       <c r="E158" s="1"/>
     </row>
     <row r="159" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>13451500</v>
+        <v>13736500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3380,7 +3387,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>1036500</v>
+        <v>1321500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="201">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -636,6 +636,12 @@
   </si>
   <si>
     <t>بستنی اسنک چیپلت</t>
+  </si>
+  <si>
+    <t>1405/06/12</t>
+  </si>
+  <si>
+    <t>بستنی ذغال</t>
   </si>
 </sst>
 </file>
@@ -763,7 +769,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1140,8 +1167,8 @@
         <v>6</v>
       </c>
       <c r="H2" s="8">
-        <f>B161</f>
-        <v>1321500</v>
+        <f>B187</f>
+        <v>1468500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3384,7 +3411,7 @@
       <c r="D159" s="8"/>
     </row>
     <row r="160" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
         <v>1321500</v>
@@ -3394,7 +3421,7 @@
       </c>
       <c r="D161" s="14"/>
     </row>
-    <row r="162" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B162" s="13" t="s">
         <v>77</v>
       </c>
@@ -3402,36 +3429,273 @@
         <v>76</v>
       </c>
     </row>
-    <row r="163" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>9</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C163" s="2"/>
+    </row>
+    <row r="164" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A164" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="7">
+        <f>B161+B165-C165</f>
+        <v>1468500</v>
+      </c>
+      <c r="B165" s="7">
+        <v>147000</v>
+      </c>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="7">
+        <f>A165+B166-C166</f>
+        <v>1468500</v>
+      </c>
+      <c r="B166" s="7"/>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="1"/>
+    </row>
+    <row r="167" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="7">
+        <f>A166+B167-C167</f>
+        <v>1468500</v>
+      </c>
+      <c r="B167" s="7"/>
+      <c r="C167" s="7"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="1"/>
+    </row>
+    <row r="168" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="7">
+        <f>A167+B168-C168</f>
+        <v>1468500</v>
+      </c>
+      <c r="B168" s="7"/>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="1"/>
+    </row>
+    <row r="169" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="7">
+        <f>A168+B169-C169</f>
+        <v>1468500</v>
+      </c>
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="1"/>
+    </row>
+    <row r="170" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="7">
+        <f t="shared" ref="A170" si="8">A169+B170-C170</f>
+        <v>1468500</v>
+      </c>
+      <c r="B170" s="7"/>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="1"/>
+    </row>
+    <row r="171" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="7">
+        <f>A170+B171-C171</f>
+        <v>1468500</v>
+      </c>
+      <c r="B171" s="7"/>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="1"/>
+    </row>
+    <row r="172" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="7">
+        <f t="shared" ref="A172:A184" si="9">A171+B172-C172</f>
+        <v>1468500</v>
+      </c>
+      <c r="B172" s="7"/>
+      <c r="C172" s="7"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="1"/>
+    </row>
+    <row r="173" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B173" s="7"/>
+      <c r="C173" s="7"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="1"/>
+    </row>
+    <row r="174" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B174" s="7"/>
+      <c r="C174" s="7"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="1"/>
+    </row>
+    <row r="175" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B175" s="7"/>
+      <c r="C175" s="7"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="1"/>
+    </row>
+    <row r="176" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B176" s="7"/>
+      <c r="C176" s="7"/>
+      <c r="D176" s="7"/>
+      <c r="E176" s="1"/>
+    </row>
+    <row r="177" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B177" s="7"/>
+      <c r="C177" s="7"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="1"/>
+    </row>
+    <row r="178" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="1"/>
+    </row>
+    <row r="179" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B179" s="7"/>
+      <c r="C179" s="7"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="1"/>
+    </row>
+    <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B180" s="7"/>
+      <c r="C180" s="7"/>
+      <c r="D180" s="7"/>
+      <c r="E180" s="1"/>
+    </row>
+    <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B181" s="7"/>
+      <c r="C181" s="7"/>
+      <c r="D181" s="7"/>
+      <c r="E181" s="1"/>
+    </row>
+    <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B182" s="7"/>
+      <c r="C182" s="7"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="1"/>
+    </row>
+    <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B183" s="7"/>
+      <c r="C183" s="7"/>
+      <c r="D183" s="7"/>
+      <c r="E183" s="1"/>
+    </row>
+    <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="7">
+        <f t="shared" si="9"/>
+        <v>1468500</v>
+      </c>
+      <c r="B184" s="7"/>
+      <c r="C184" s="7"/>
+      <c r="D184" s="7"/>
+      <c r="E184" s="1"/>
+    </row>
+    <row r="185" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="8"/>
+      <c r="B185" s="8">
+        <f>SUM(B165:B184)+B159</f>
+        <v>13883500</v>
+      </c>
+      <c r="C185" s="8">
+        <f>SUM(C165:C184)+C159</f>
+        <v>12415000</v>
+      </c>
+      <c r="D185" s="8"/>
+    </row>
+    <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B187" s="11">
+        <f>A184</f>
+        <v>1468500</v>
+      </c>
+      <c r="C187" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D187" s="14"/>
+    </row>
+    <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B188" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D188" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="193" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="194" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="195" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3455,35 +3719,47 @@
     <row r="213" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="214" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="C82:D82"/>
     <mergeCell ref="C109:D109"/>
     <mergeCell ref="C135:D135"/>
     <mergeCell ref="C161:D161"/>
+    <mergeCell ref="C187:D187"/>
   </mergeCells>
   <conditionalFormatting sqref="B109">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B135">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B161">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B161">
+  <conditionalFormatting sqref="B187">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
